--- a/EC Scenarios/Applied_ECs.xlsx
+++ b/EC Scenarios/Applied_ECs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="186">
   <si>
     <t>Scenario</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Spent Time by LLM4ECM ?</t>
   </si>
   <si>
+    <t>Spent Time by Direct Text-to-AML?</t>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
@@ -58,6 +61,9 @@
     <t>13 Min</t>
   </si>
   <si>
+    <t>2 Min</t>
+  </si>
+  <si>
     <t>Update and increase the rotational speed of PS2_Pumpe from 100.0 rpm to 150.0 rpm.</t>
   </si>
   <si>
@@ -70,6 +76,9 @@
     <t>93 %</t>
   </si>
   <si>
+    <t>3 Min</t>
+  </si>
+  <si>
     <t>Update the rotational speed of reactor TS to 10.0 rpm.</t>
   </si>
   <si>
@@ -109,6 +118,9 @@
     <t>90 %</t>
   </si>
   <si>
+    <t>70 %</t>
+  </si>
+  <si>
     <t>Delete PR_Pumpe from AML model and all its Relations</t>
   </si>
   <si>
@@ -121,6 +133,9 @@
     <t>10 Min</t>
   </si>
   <si>
+    <t>1 Min</t>
+  </si>
+  <si>
     <t>Add a tank with Name Tank5_T5 with pressure 1.0 kPa, temperature 25.0 °C and level 25.0 cm.</t>
   </si>
   <si>
@@ -136,6 +151,12 @@
     <t>11 Min</t>
   </si>
   <si>
+    <t>4Min</t>
+  </si>
+  <si>
+    <t>80 %</t>
+  </si>
+  <si>
     <t>Replace level sensor SD_L2_T4 with a temperature sensor with this name SC_T1_T4 for Tank4_T4</t>
   </si>
   <si>
@@ -145,6 +166,15 @@
     <t>26 Min</t>
   </si>
   <si>
+    <t>4 Min</t>
+  </si>
+  <si>
+    <t>81 %</t>
+  </si>
+  <si>
+    <t>73 %</t>
+  </si>
+  <si>
     <t>C3</t>
   </si>
   <si>
@@ -163,6 +193,15 @@
     <t>20 Min</t>
   </si>
   <si>
+    <t>5 Min</t>
+  </si>
+  <si>
+    <t>78 %</t>
+  </si>
+  <si>
+    <t>71 %</t>
+  </si>
+  <si>
     <t>Add a tank with Name Tank5_T5 with pressure 5.0 kPa, temperature 35.0 °C and level 25.0 cm and add a pipe with pressure 5.0 kPa, temperature 35.0 °C and flow 20.0 m³/h  titeld Pipe_T1_T5 between Tank1_T1 and Tank5_T5.</t>
   </si>
   <si>
@@ -172,6 +211,12 @@
     <t>39 Min</t>
   </si>
   <si>
+    <t>65 %</t>
+  </si>
+  <si>
+    <t>67 %</t>
+  </si>
+  <si>
     <t>Define the attribute material Steel  and for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, add capacity 20.0 m³ for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, update the pressure of Tank1_T1 to 5.0 kPa.</t>
   </si>
   <si>
@@ -184,6 +229,12 @@
     <t>21 Min</t>
   </si>
   <si>
+    <t>61 %</t>
+  </si>
+  <si>
+    <t>60  %</t>
+  </si>
+  <si>
     <t>Put SC_PH1_T1 as meter for measuring PH in Tank1_T1 instead of levelmeter SD_L1_T1 and Add the attribute "voltage" with a value of 220.0 V to this sensor</t>
   </si>
   <si>
@@ -274,6 +325,9 @@
     <t>25 Min</t>
   </si>
   <si>
+    <t>83 %</t>
+  </si>
+  <si>
     <t>Add the attribute "material" with value stainless steel to PR_Pumpe and increase the pressure of Pipe_PR to 2.2 kPa.</t>
   </si>
   <si>
@@ -283,6 +337,9 @@
     <t>30 Min</t>
   </si>
   <si>
+    <t>79 %</t>
+  </si>
+  <si>
     <t>Add a tank named Tank6_T6 with pressure 2.0 kPa, temperature 22.0 °C, and level 40.0 cm, and connect it to PB via a new pipe Pipe_PB_T6 with flow 0.8 m³/h.</t>
   </si>
   <si>
@@ -301,6 +358,9 @@
     <t>36 Min</t>
   </si>
   <si>
+    <t>63 %</t>
+  </si>
+  <si>
     <t>Replace the level sensor SD_L4_TB with a pH sensor SC_PH2_TB and update the pressure of Pipe_V1_TB_SV1_TBRC to 4.0 kPa.</t>
   </si>
   <si>
@@ -343,6 +403,9 @@
     <t>EC29.json</t>
   </si>
   <si>
+    <t>82 %</t>
+  </si>
+  <si>
     <t>Delete the pipe Pipe_V1_T3TB_TB and remove all its relations.</t>
   </si>
   <si>
@@ -364,6 +427,9 @@
     <t>EC32.json</t>
   </si>
   <si>
+    <t>86 %</t>
+  </si>
+  <si>
     <t>Delete valve AD_V1_PBTM and assign a voltage attribute of 220.0 V to pump PS2_Pumpe.</t>
   </si>
   <si>
@@ -385,9 +451,6 @@
     <t>EC35.json</t>
   </si>
   <si>
-    <t>80 %</t>
-  </si>
-  <si>
     <t>Add a new tank T6_Tank with level 30.0 cm and connect it to PS2_Pumpe via a new pipe Pipe_PS2_T6 with flow 0.6 m3/h.</t>
   </si>
   <si>
@@ -460,12 +523,6 @@
     <t>EC46.json</t>
   </si>
   <si>
-    <t>65 %</t>
-  </si>
-  <si>
-    <t>70 %</t>
-  </si>
-  <si>
     <t>Increase the pressure of PR_Pumpe to 2kPa and delete the temperature attribute for PR_Pumpe</t>
   </si>
   <si>
@@ -475,12 +532,18 @@
     <t>34 Min</t>
   </si>
   <si>
+    <t>75 %</t>
+  </si>
+  <si>
     <t>Add new attributes capacity 29.0 m³ and material steel  for Tank2_T2 withput presentation of level attribute.</t>
   </si>
   <si>
     <t>EC48.json</t>
   </si>
   <si>
+    <t>74 %</t>
+  </si>
+  <si>
     <t>Avg = 22.71 Min</t>
   </si>
   <si>
@@ -497,6 +560,15 @@
   </si>
   <si>
     <t>Avg = 98.77 %</t>
+  </si>
+  <si>
+    <t>Avg = 2.65 Min</t>
+  </si>
+  <si>
+    <t>Avg =  89.50 %</t>
+  </si>
+  <si>
+    <t>Avg = 87.69 %</t>
   </si>
 </sst>
 </file>
@@ -526,7 +598,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -549,6 +621,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
         <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -589,42 +667,42 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="6" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -861,7 +939,10 @@
     <col customWidth="1" min="7" max="7" width="17.5"/>
     <col customWidth="1" min="8" max="8" width="23.13"/>
     <col customWidth="1" min="9" max="9" width="21.75"/>
-    <col customWidth="1" min="10" max="10" width="16.0"/>
+    <col customWidth="1" min="10" max="10" width="17.63"/>
+    <col customWidth="1" min="11" max="11" width="29.75"/>
+    <col customWidth="1" min="12" max="12" width="16.75"/>
+    <col customWidth="1" min="13" max="13" width="19.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,1590 +976,1983 @@
       <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="6"/>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="6"/>
+      <c r="I3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="6"/>
+      <c r="L4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="I6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>40</v>
+      <c r="A8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="I8" s="7">
         <v>0.9</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="F15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="F18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="J21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="J23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="L24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="B25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="I25" s="7">
         <v>0.93</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="F29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="F35" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="L39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="F42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="I42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
+      <c r="F43" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K36" s="6"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="6"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="6"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="6"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K40" s="6"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K41" s="6"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="I43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M43" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F43" s="4" t="s">
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>129</v>
+      <c r="B44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>18</v>
+        <v>163</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G44" s="7">
         <v>0.95</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K44" s="6"/>
+      <c r="H44" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K45" s="6"/>
+      <c r="A45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="G46" s="7">
         <v>0.93</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" s="6"/>
+      <c r="H46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="J48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" s="6"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K48" s="6"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K49" s="6"/>
+      <c r="E49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -2491,6 +2965,9 @@
       <c r="H50" s="12"/>
       <c r="I50" s="13"/>
       <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="12"/>
     </row>
     <row r="51" ht="32.25" customHeight="1">
       <c r="A51" s="11"/>
@@ -2498,22 +2975,31 @@
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
       <c r="E51" s="14" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>161</v>
+        <v>182</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="M51" s="14" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="52">

--- a/EC Scenarios/Applied_ECs.xlsx
+++ b/EC Scenarios/Applied_ECs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="194">
   <si>
     <t>Scenario</t>
   </si>
@@ -61,450 +61,456 @@
     <t>100 %</t>
   </si>
   <si>
-    <t>6 Min</t>
+    <t>10 Min</t>
+  </si>
+  <si>
+    <t>12 Min</t>
+  </si>
+  <si>
+    <t>13 Min</t>
+  </si>
+  <si>
+    <t>Update and increase the rotational speed of PS2_Pumpe from 100.0 rpm to 150.0 rpm.</t>
+  </si>
+  <si>
+    <t>EC02.json</t>
+  </si>
+  <si>
+    <t>93 %</t>
+  </si>
+  <si>
+    <t>91 %</t>
+  </si>
+  <si>
+    <t>Update the rotational speed of reactor TS to 10.0 rpm.</t>
+  </si>
+  <si>
+    <t>EC03.json</t>
+  </si>
+  <si>
+    <t>18 Min</t>
+  </si>
+  <si>
+    <t>73 %</t>
+  </si>
+  <si>
+    <t>81 %</t>
+  </si>
+  <si>
+    <t>11 Min</t>
+  </si>
+  <si>
+    <t>90 %</t>
+  </si>
+  <si>
+    <t>14 Min</t>
+  </si>
+  <si>
+    <t>Increase the pressure of pipe Pipe_PR_Ventil to 2kPa.</t>
+  </si>
+  <si>
+    <t>EC04.json</t>
+  </si>
+  <si>
+    <t>17 Min</t>
+  </si>
+  <si>
+    <t>87 %</t>
+  </si>
+  <si>
+    <t>95 %</t>
+  </si>
+  <si>
+    <t>85 %</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Add the attribute "voltage" with a value of 220.0 V to PS2_Pumpe.</t>
+  </si>
+  <si>
+    <t>EC05.json</t>
+  </si>
+  <si>
+    <t>60 %</t>
+  </si>
+  <si>
+    <t>66 %</t>
+  </si>
+  <si>
+    <t>15 Min</t>
+  </si>
+  <si>
+    <t>97 %</t>
+  </si>
+  <si>
+    <t>98 %</t>
+  </si>
+  <si>
+    <t>Delete PR_Pumpe from AML model and all its Relations</t>
+  </si>
+  <si>
+    <t>EC06.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Min </t>
   </si>
   <si>
     <t>9 Min</t>
   </si>
   <si>
-    <t>13 Min</t>
-  </si>
-  <si>
-    <t>Update and increase the rotational speed of PS2_Pumpe from 100.0 rpm to 150.0 rpm.</t>
-  </si>
-  <si>
-    <t>EC02.json</t>
-  </si>
-  <si>
-    <t>12 Min</t>
-  </si>
-  <si>
-    <t>93 %</t>
+    <t>Add a tank with Name Tank5_T5 with pressure 1.0 kPa, temperature 25.0 °C and level 25.0 cm.</t>
+  </si>
+  <si>
+    <t>EC07.json</t>
+  </si>
+  <si>
+    <t>19 Min</t>
+  </si>
+  <si>
+    <t>71 %</t>
+  </si>
+  <si>
+    <t>76 %</t>
+  </si>
+  <si>
+    <t>82 %</t>
+  </si>
+  <si>
+    <t>Replace level sensor SD_L2_T4 with a temperature sensor with this name SC_T1_T4 for Tank4_T4</t>
+  </si>
+  <si>
+    <t>EC08.json</t>
+  </si>
+  <si>
+    <t>26 Min</t>
+  </si>
+  <si>
+    <t>65 %</t>
+  </si>
+  <si>
+    <t>69 %</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Add a new attribute, "weight", with a value of 80.0 kg to Tank2_T2, and update the pressure of Tank1_T1 to 5 kPa.</t>
+  </si>
+  <si>
+    <t>EC09.json</t>
+  </si>
+  <si>
+    <t>35 Min</t>
+  </si>
+  <si>
+    <t>61 %</t>
+  </si>
+  <si>
+    <t>67 %</t>
+  </si>
+  <si>
+    <t>96 %</t>
+  </si>
+  <si>
+    <t>20 Min</t>
+  </si>
+  <si>
+    <t>Add a tank with Name Tank5_T5 with pressure 5.0 kPa, temperature 35.0 °C and level 25.0 cm and add a pipe with pressure 5.0 kPa, temperature 35.0 °C and flow 20.0 m³/h  titeld Pipe_T1_T5 between Tank1_T1 and Tank5_T5.</t>
+  </si>
+  <si>
+    <t>EC10.json</t>
+  </si>
+  <si>
+    <t>39 Min</t>
+  </si>
+  <si>
+    <t>56 %</t>
+  </si>
+  <si>
+    <t>63 %</t>
+  </si>
+  <si>
+    <t>Define the attribute material Steel  and for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, add capacity 20.0 m³ for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, update the pressure of Tank1_T1 to 5.0 kPa.</t>
+  </si>
+  <si>
+    <t>EC11.json</t>
+  </si>
+  <si>
+    <t>45 Min</t>
+  </si>
+  <si>
+    <t>52 %</t>
+  </si>
+  <si>
+    <t>92 %</t>
+  </si>
+  <si>
+    <t>21 Min</t>
+  </si>
+  <si>
+    <t>Put SC_PH1_T1 as meter for measuring PH in Tank1_T1 instead of levelmeter SD_L1_T1 and Add the attribute "voltage" with a value of 220.0 V to this sensor</t>
+  </si>
+  <si>
+    <t>EC12.json</t>
+  </si>
+  <si>
+    <t>33 Min</t>
+  </si>
+  <si>
+    <t>88 %</t>
+  </si>
+  <si>
+    <t>Update the pressure of Pipe_V1_PRT1_T1 from 1.0 kPa to 1.8 kPa.</t>
+  </si>
+  <si>
+    <t>EC13.json</t>
+  </si>
+  <si>
+    <t>Expert 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 % </t>
+  </si>
+  <si>
+    <t>Decrease the temperature of Pipe_TW_HV1_TW from 20.0 °C to 12.0 °C.</t>
+  </si>
+  <si>
+    <t>EC14.json</t>
   </si>
   <si>
     <t>8 Min</t>
   </si>
   <si>
-    <t>10 Min</t>
-  </si>
-  <si>
-    <t>Update the rotational speed of reactor TS to 10.0 rpm.</t>
-  </si>
-  <si>
-    <t>EC03.json</t>
-  </si>
-  <si>
-    <t>18 Min</t>
-  </si>
-  <si>
-    <t>88 %</t>
-  </si>
-  <si>
-    <t>14 Min</t>
-  </si>
-  <si>
-    <t>Increase the pressure of pipe Pipe_PR_Ventil to 2kPa.</t>
-  </si>
-  <si>
-    <t>EC04.json</t>
-  </si>
-  <si>
-    <t>17 Min</t>
-  </si>
-  <si>
-    <t>87 %</t>
+    <t>94 %</t>
+  </si>
+  <si>
+    <t>Open the valve AD_V1_T2TB partially and update its state from 14% to 75%.</t>
+  </si>
+  <si>
+    <t>EC15.json</t>
+  </si>
+  <si>
+    <t>84 %</t>
+  </si>
+  <si>
+    <t>89 %</t>
+  </si>
+  <si>
+    <t>Increase the flow rate of Pipe_TB_V1_TB from 2.0 m³/h to 3.0 m³/h.</t>
+  </si>
+  <si>
+    <t>EC16.json</t>
+  </si>
+  <si>
+    <t>Add the attribute "voltage" with a value of 24.0 V to SC_PH1_T4_pH.</t>
+  </si>
+  <si>
+    <t>EC17.json</t>
+  </si>
+  <si>
+    <t>Delete AD_V1_PSTB from the AML model and remove all its relations.</t>
+  </si>
+  <si>
+    <t>EC18.json</t>
+  </si>
+  <si>
+    <t>23 Min</t>
+  </si>
+  <si>
+    <t>Add a pipe named Pipe_T4_TB between Tank4_T4 and TB with pressure 3.0 kPa, temperature 30.0 °C, and flow 1.5 m³/h.</t>
+  </si>
+  <si>
+    <t>EC19.json</t>
+  </si>
+  <si>
+    <t>22 Min</t>
+  </si>
+  <si>
+    <t>Replace the level sensor SD_L3_TB with a pH sensor named SC_PH2_TB for TB.</t>
+  </si>
+  <si>
+    <t>EC20.json</t>
+  </si>
+  <si>
+    <t>25 Min</t>
+  </si>
+  <si>
+    <t>74 %</t>
+  </si>
+  <si>
+    <t>Add the attribute "material" with value stainless steel to PR_Pumpe and increase the pressure of Pipe_PR to 2.2 kPa.</t>
+  </si>
+  <si>
+    <t>EC21.json</t>
+  </si>
+  <si>
+    <t>30 Min</t>
+  </si>
+  <si>
+    <t>70 %</t>
+  </si>
+  <si>
+    <t>77 %</t>
+  </si>
+  <si>
+    <t>Add a tank named Tank6_T6 with pressure 2.0 kPa, temperature 22.0 °C, and level 40.0 cm, and connect it to PB via a new pipe Pipe_PB_T6 with flow 0.8 m³/h.</t>
+  </si>
+  <si>
+    <t>EC22.json</t>
+  </si>
+  <si>
+    <t>28 Min</t>
+  </si>
+  <si>
+    <t>Replace AD_V1_PBTM with a continuously controlled valve AC_SV1_PBTM, keep the existing connections to Pipe_V1_PBTM_TM, and add voltage 220.0 V.</t>
+  </si>
+  <si>
+    <t>EC23.json</t>
+  </si>
+  <si>
+    <t>36 Min</t>
+  </si>
+  <si>
+    <t>Replace the level sensor SD_L4_TB with a pH sensor SC_PH2_TB and update the pressure of Pipe_V1_TB_SV1_TBRC to 4.0 kPa.</t>
+  </si>
+  <si>
+    <t>EC24.json</t>
+  </si>
+  <si>
+    <t>40 Min</t>
+  </si>
+  <si>
+    <t>Increase the pressure of Pipe_V1_T3TM_TM from 1.0 kPa to 2.5 kPa.</t>
+  </si>
+  <si>
+    <t>EC25.json</t>
+  </si>
+  <si>
+    <t>Expert 3</t>
+  </si>
+  <si>
+    <t>Reduce the rotational speed of PS1_Pumpe from 12.0 rpm to 9.0 rpm.</t>
+  </si>
+  <si>
+    <t>EC26.json</t>
+  </si>
+  <si>
+    <t>Change the state of AD_V1_T4TS from 14% to 70%.</t>
+  </si>
+  <si>
+    <t>EC27.json</t>
+  </si>
+  <si>
+    <t>Update the temperature of K1_Product_Side from 20.0 C to 8.0 C.</t>
+  </si>
+  <si>
+    <t>EC28.json</t>
+  </si>
+  <si>
+    <t>Add a ph measurement to SC_PH1_T3_pH with value 6.8</t>
+  </si>
+  <si>
+    <t>EC29.json</t>
+  </si>
+  <si>
+    <t>79 %</t>
+  </si>
+  <si>
+    <t>Delete the pipe Pipe_V1_T3TB_TB and remove all its relations.</t>
+  </si>
+  <si>
+    <t>EC30.json</t>
   </si>
   <si>
     <t>7 Min</t>
   </si>
   <si>
-    <t>78 %</t>
-  </si>
-  <si>
-    <t>92 %</t>
-  </si>
-  <si>
-    <t>85 %</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>Add the attribute "voltage" with a value of 220.0 V to PS2_Pumpe.</t>
-  </si>
-  <si>
-    <t>EC05.json</t>
-  </si>
-  <si>
-    <t>90 %</t>
-  </si>
-  <si>
-    <t>66 %</t>
-  </si>
-  <si>
-    <t>95 %</t>
-  </si>
-  <si>
-    <t>Delete PR_Pumpe from AML model and all its Relations</t>
-  </si>
-  <si>
-    <t>EC06.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Min </t>
-  </si>
-  <si>
-    <t>5 Min</t>
-  </si>
-  <si>
-    <t>Add a tank with Name Tank5_T5 with pressure 1.0 kPa, temperature 25.0 °C and level 25.0 cm.</t>
-  </si>
-  <si>
-    <t>EC07.json</t>
-  </si>
-  <si>
-    <t>19 Min</t>
-  </si>
-  <si>
-    <t>74 %</t>
-  </si>
-  <si>
-    <t>76 %</t>
+    <t>Delete the sensor SD_L3_TB and remove all its relations.</t>
+  </si>
+  <si>
+    <t>EC31.json</t>
   </si>
   <si>
     <t>80 %</t>
   </si>
   <si>
-    <t>94 %</t>
-  </si>
-  <si>
-    <t>11 Min</t>
-  </si>
-  <si>
-    <t>Replace level sensor SD_L2_T4 with a temperature sensor with this name SC_T1_T4 for Tank4_T4</t>
-  </si>
-  <si>
-    <t>EC08.json</t>
-  </si>
-  <si>
-    <t>26 Min</t>
+    <t>Add a new pipe Pipe_X1_TB between X1 and TB  with pressure 2.0 kPa, temperature 25.0 °C, and flow 3 m³/h.</t>
+  </si>
+  <si>
+    <t>EC32.json</t>
   </si>
   <si>
     <t>75 %</t>
   </si>
   <si>
-    <t>69 %</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Add a new attribute, "weight", with a value of 80.0 kg to Tank2_T2, and update the pressure of Tank1_T1 to 5 kPa.</t>
-  </si>
-  <si>
-    <t>EC09.json</t>
-  </si>
-  <si>
-    <t>35 Min</t>
-  </si>
-  <si>
-    <t>97 %</t>
+    <t>Delete valve AD_V1_PBTM and assign a voltage attribute of 220.0 V to pump PS2_Pumpe.</t>
+  </si>
+  <si>
+    <t>EC33.json</t>
+  </si>
+  <si>
+    <t>Increase the rotational speed of TB to 400rpm and delete the temperature attribute for Tank3_T3</t>
+  </si>
+  <si>
+    <t>EC34.json</t>
   </si>
   <si>
     <t>72 %</t>
   </si>
   <si>
-    <t>67 %</t>
-  </si>
-  <si>
-    <t>20 Min</t>
-  </si>
-  <si>
-    <t>Add a tank with Name Tank5_T5 with pressure 5.0 kPa, temperature 35.0 °C and level 25.0 cm and add a pipe with pressure 5.0 kPa, temperature 35.0 °C and flow 20.0 m³/h  titeld Pipe_T1_T5 between Tank1_T1 and Tank5_T5.</t>
-  </si>
-  <si>
-    <t>EC10.json</t>
-  </si>
-  <si>
-    <t>39 Min</t>
-  </si>
-  <si>
-    <t>59 %</t>
-  </si>
-  <si>
-    <t>63 %</t>
-  </si>
-  <si>
-    <t>15 Min</t>
-  </si>
-  <si>
-    <t>Define the attribute material Steel  and for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, add capacity 20.0 m³ for Tank1_T1, Tank2_T2, Tank3_T3, Tank4_T4, update the pressure of Tank1_T1 to 5.0 kPa.</t>
-  </si>
-  <si>
-    <t>EC11.json</t>
-  </si>
-  <si>
-    <t>45 Min</t>
-  </si>
-  <si>
-    <t>55 %</t>
-  </si>
-  <si>
-    <t>56 %</t>
-  </si>
-  <si>
-    <t>21 Min</t>
-  </si>
-  <si>
-    <t>Put SC_PH1_T1 as meter for measuring PH in Tank1_T1 instead of levelmeter SD_L1_T1 and Add the attribute "voltage" with a value of 220.0 V to this sensor</t>
-  </si>
-  <si>
-    <t>EC12.json</t>
-  </si>
-  <si>
-    <t>33 Min</t>
+    <t>Add the attribute "voltage" with a value of 220.0 V to AC_SV1_T2 and set its state to 50%.</t>
+  </si>
+  <si>
+    <t>EC35.json</t>
+  </si>
+  <si>
+    <t>Add a new tank T6_Tank with level 30.0 cm and connect it to PS2_Pumpe via a new pipe Pipe_PS2_T6 with flow 0.6 m3/h.</t>
+  </si>
+  <si>
+    <t>EC36.json</t>
+  </si>
+  <si>
+    <t>64 %</t>
+  </si>
+  <si>
+    <t>Increae and update the flow rate of AD_V1_T3TB valve from 1.0 m³/h to 2.5 m³/h.</t>
+  </si>
+  <si>
+    <t>EC37.json</t>
+  </si>
+  <si>
+    <t>Expert 4</t>
+  </si>
+  <si>
+    <t>Close the valve AD_V1_PRT4 and change its state to 0%.</t>
+  </si>
+  <si>
+    <t>EC38.json</t>
+  </si>
+  <si>
+    <t>Reduce and change the temperature of Condensers of K1_Product_Side and K2_Product_Side to 5.0 °C</t>
+  </si>
+  <si>
+    <t>EC39.json</t>
+  </si>
+  <si>
+    <t>Open completely the control valve AC_SV1_T2 and update the its state to 100 %.</t>
+  </si>
+  <si>
+    <t>EC40.json</t>
+  </si>
+  <si>
+    <t>Add the attribute "voltage" with a value of 220.0 V to continuesly control valve AC_SV1_T2 and AC_SV1_TBRC.</t>
+  </si>
+  <si>
+    <t>EC41.json</t>
   </si>
   <si>
     <t>86 %</t>
   </si>
   <si>
-    <t>89 %</t>
-  </si>
-  <si>
-    <t>Update the pressure of Pipe_V1_PRT1_T1 from 1.0 kPa to 1.8 kPa.</t>
-  </si>
-  <si>
-    <t>EC13.json</t>
-  </si>
-  <si>
-    <t>Expert 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 % </t>
-  </si>
-  <si>
-    <t>Decrease the temperature of Pipe_TW_HV1_TW from 20.0 °C to 12.0 °C.</t>
-  </si>
-  <si>
-    <t>EC14.json</t>
-  </si>
-  <si>
-    <t>Open the valve AD_V1_T2TB partially and update its state from 14% to 75%.</t>
-  </si>
-  <si>
-    <t>EC15.json</t>
-  </si>
-  <si>
-    <t>84 %</t>
-  </si>
-  <si>
-    <t>Increase the flow rate of Pipe_TB_V1_TB from 2.0 m³/h to 3.0 m³/h.</t>
-  </si>
-  <si>
-    <t>EC16.json</t>
-  </si>
-  <si>
-    <t>Add the attribute "voltage" with a value of 24.0 V to SC_PH1_T4_pH.</t>
-  </si>
-  <si>
-    <t>EC17.json</t>
-  </si>
-  <si>
-    <t>91 %</t>
-  </si>
-  <si>
-    <t>Delete AD_V1_PSTB from the AML model and remove all its relations.</t>
-  </si>
-  <si>
-    <t>EC18.json</t>
-  </si>
-  <si>
-    <t>23 Min</t>
-  </si>
-  <si>
-    <t>4 Min</t>
-  </si>
-  <si>
-    <t>Add a pipe named Pipe_T4_TB between Tank4_T4 and TB with pressure 3.0 kPa, temperature 30.0 °C, and flow 1.5 m³/h.</t>
-  </si>
-  <si>
-    <t>EC19.json</t>
-  </si>
-  <si>
-    <t>22 Min</t>
-  </si>
-  <si>
-    <t>79 %</t>
-  </si>
-  <si>
-    <t>Replace the level sensor SD_L3_TB with a pH sensor named SC_PH2_TB for TB.</t>
-  </si>
-  <si>
-    <t>EC20.json</t>
-  </si>
-  <si>
-    <t>25 Min</t>
-  </si>
-  <si>
-    <t>77 %</t>
-  </si>
-  <si>
-    <t>81 %</t>
-  </si>
-  <si>
-    <t>Add the attribute "material" with value stainless steel to PR_Pumpe and increase the pressure of Pipe_PR to 2.2 kPa.</t>
-  </si>
-  <si>
-    <t>EC21.json</t>
-  </si>
-  <si>
-    <t>30 Min</t>
-  </si>
-  <si>
-    <t>73 %</t>
-  </si>
-  <si>
-    <t>Add a tank named Tank6_T6 with pressure 2.0 kPa, temperature 22.0 °C, and level 40.0 cm, and connect it to PB via a new pipe Pipe_PB_T6 with flow 0.8 m³/h.</t>
-  </si>
-  <si>
-    <t>EC22.json</t>
-  </si>
-  <si>
-    <t>28 Min</t>
-  </si>
-  <si>
-    <t>61 %</t>
-  </si>
-  <si>
-    <t>Replace AD_V1_PBTM with a continuously controlled valve AC_SV1_PBTM, keep the existing connections to Pipe_V1_PBTM_TM, and add voltage 220.0 V.</t>
-  </si>
-  <si>
-    <t>EC23.json</t>
-  </si>
-  <si>
-    <t>36 Min</t>
-  </si>
-  <si>
-    <t>Replace the level sensor SD_L4_TB with a pH sensor SC_PH2_TB and update the pressure of Pipe_V1_TB_SV1_TBRC to 4.0 kPa.</t>
-  </si>
-  <si>
-    <t>EC24.json</t>
-  </si>
-  <si>
-    <t>40 Min</t>
-  </si>
-  <si>
-    <t>Increase the pressure of Pipe_V1_T3TM_TM from 1.0 kPa to 2.5 kPa.</t>
-  </si>
-  <si>
-    <t>EC25.json</t>
-  </si>
-  <si>
-    <t>Expert 3</t>
-  </si>
-  <si>
-    <t>Reduce the rotational speed of PS1_Pumpe from 12.0 rpm to 9.0 rpm.</t>
-  </si>
-  <si>
-    <t>EC26.json</t>
-  </si>
-  <si>
-    <t>Change the state of AD_V1_T4TS from 14% to 70%.</t>
-  </si>
-  <si>
-    <t>EC27.json</t>
-  </si>
-  <si>
-    <t>Update the temperature of K1_Product_Side from 20.0 C to 8.0 C.</t>
-  </si>
-  <si>
-    <t>EC28.json</t>
-  </si>
-  <si>
-    <t>Add a ph measurement to SC_PH1_T3_pH with value 6.8</t>
-  </si>
-  <si>
-    <t>EC29.json</t>
-  </si>
-  <si>
-    <t>Delete the pipe Pipe_V1_T3TB_TB and remove all its relations.</t>
-  </si>
-  <si>
-    <t>EC30.json</t>
-  </si>
-  <si>
-    <t>Delete the sensor SD_L3_TB and remove all its relations.</t>
-  </si>
-  <si>
-    <t>EC31.json</t>
-  </si>
-  <si>
-    <t>Add a new pipe Pipe_X1_TB between X1 and TB  with pressure 2.0 kPa, temperature 25.0 °C, and flow 3 m³/h.</t>
-  </si>
-  <si>
-    <t>EC32.json</t>
-  </si>
-  <si>
-    <t>82 %</t>
-  </si>
-  <si>
-    <t>Delete valve AD_V1_PBTM and assign a voltage attribute of 220.0 V to pump PS2_Pumpe.</t>
-  </si>
-  <si>
-    <t>EC33.json</t>
-  </si>
-  <si>
-    <t>Increase the rotational speed of TB to 400rpm and delete the temperature attribute for Tank3_T3</t>
-  </si>
-  <si>
-    <t>EC34.json</t>
-  </si>
-  <si>
-    <t>Add the attribute "voltage" with a value of 220.0 V to AC_SV1_T2 and set its state to 50%.</t>
-  </si>
-  <si>
-    <t>EC35.json</t>
-  </si>
-  <si>
-    <t>Add a new tank T6_Tank with level 30.0 cm and connect it to PS2_Pumpe via a new pipe Pipe_PS2_T6 with flow 0.6 m3/h.</t>
-  </si>
-  <si>
-    <t>EC36.json</t>
-  </si>
-  <si>
-    <t>Increae and update the flow rate of AD_V1_T3TB valve from 1.0 m³/h to 2.5 m³/h.</t>
-  </si>
-  <si>
-    <t>EC37.json</t>
-  </si>
-  <si>
-    <t>Expert 4</t>
-  </si>
-  <si>
-    <t>Close the valve AD_V1_PRT4 and change its state to 0%.</t>
-  </si>
-  <si>
-    <t>EC38.json</t>
-  </si>
-  <si>
-    <t>Reduce and change the temperature of Condensers of K1_Product_Side and K2_Product_Side to 5.0 °C</t>
-  </si>
-  <si>
-    <t>EC39.json</t>
-  </si>
-  <si>
-    <t>Open completely the control valve AC_SV1_T2 and update the its state to 100 %.</t>
-  </si>
-  <si>
-    <t>EC40.json</t>
-  </si>
-  <si>
-    <t>Add the attribute "voltage" with a value of 220.0 V to continuesly control valve AC_SV1_T2 and AC_SV1_TBRC.</t>
-  </si>
-  <si>
-    <t>EC41.json</t>
-  </si>
-  <si>
     <t>Replace SC_PH1_T1 as meter for measuring PH to Tank1_T1 instead of SD_L2_T1 and SC_PH1_T2 as meter for measuring PH to Tank2_T2 instead of SC_L1_T2_Fuellstand.</t>
   </si>
   <si>
@@ -526,9 +532,6 @@
     <t>EC44.json</t>
   </si>
   <si>
-    <t>64 %</t>
-  </si>
-  <si>
     <t>Replace the valve AD_V1_PBT2 with a continuesly control valve AC_SV2_T2 with same attributes and relationships</t>
   </si>
   <si>
@@ -541,12 +544,6 @@
     <t>EC46.json</t>
   </si>
   <si>
-    <t>65 %</t>
-  </si>
-  <si>
-    <t>70 %</t>
-  </si>
-  <si>
     <t>Increase the pressure of PR_Pumpe to 2kPa and delete the temperature attribute for PR_Pumpe</t>
   </si>
   <si>
@@ -556,9 +553,6 @@
     <t>34 Min</t>
   </si>
   <si>
-    <t>71 %</t>
-  </si>
-  <si>
     <t>Add new attributes capacity 29.0 m³ and material steel  for Tank2_T2 withput presentation of level attribute.</t>
   </si>
   <si>
@@ -574,22 +568,22 @@
     <t>Avg = 96.27 %</t>
   </si>
   <si>
-    <t>Avg = 6.06 Min</t>
-  </si>
-  <si>
-    <t>Avg =  86.52 %</t>
-  </si>
-  <si>
-    <t>Avg =  85.69 %</t>
-  </si>
-  <si>
-    <t>Avg =  8.98 Min</t>
-  </si>
-  <si>
-    <t>Avg =  90.35 %</t>
-  </si>
-  <si>
-    <t>Avg = 93.46 %</t>
+    <t>Avg = 10.06 Min</t>
+  </si>
+  <si>
+    <t>Avg =  79.08 %</t>
+  </si>
+  <si>
+    <t>Avg =  83.83 %</t>
+  </si>
+  <si>
+    <t>Avg =  11.98 Min</t>
+  </si>
+  <si>
+    <t>Avg =  92.44 %</t>
+  </si>
+  <si>
+    <t>Avg = 96.29 %</t>
   </si>
   <si>
     <t>Avg = 13.27 Min</t>
@@ -655,8 +649,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8E7CC3"/>
-        <bgColor rgb="FF8E7CC3"/>
+        <fgColor rgb="FFB4A7D6"/>
+        <bgColor rgb="FFB4A7D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1095,25 +1089,25 @@
         <v>13</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="J3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>15</v>
@@ -1136,46 +1130,46 @@
         <v>10</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="K4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="N4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>15</v>
@@ -1186,25 +1180,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>15</v>
@@ -1216,16 +1210,16 @@
         <v>17</v>
       </c>
       <c r="L5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>15</v>
@@ -1233,46 +1227,46 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>43</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>15</v>
@@ -1283,19 +1277,19 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>15</v>
@@ -1304,7 +1298,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>15</v>
@@ -1313,7 +1307,7 @@
         <v>15</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>15</v>
@@ -1322,7 +1316,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>15</v>
@@ -1333,46 +1327,46 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O8" s="8">
         <v>0.9</v>
@@ -1383,46 +1377,46 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="K9" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>15</v>
@@ -1433,46 +1427,46 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="K10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="M10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>15</v>
@@ -1483,46 +1477,46 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="K11" s="6" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>15</v>
@@ -1533,46 +1527,46 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="6" t="s">
+      <c r="M12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>15</v>
@@ -1583,28 +1577,28 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>15</v>
@@ -1613,16 +1607,16 @@
         <v>15</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>15</v>
@@ -1636,34 +1630,34 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="G14" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>15</v>
@@ -1672,7 +1666,7 @@
         <v>15</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>15</v>
@@ -1686,46 +1680,46 @@
         <v>10</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="J15" s="6" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>15</v>
@@ -1736,25 +1730,25 @@
         <v>10</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>15</v>
@@ -1763,22 +1757,22 @@
         <v>15</v>
       </c>
       <c r="K16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="O16" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1792,40 +1786,40 @@
         <v>96</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>15</v>
@@ -1833,7 +1827,7 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>97</v>
@@ -1842,40 +1836,40 @@
         <v>98</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="L18" s="6" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>15</v>
@@ -1883,20 +1877,20 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="F19" s="6" t="s">
         <v>15</v>
       </c>
@@ -1904,7 +1898,7 @@
         <v>15</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>15</v>
@@ -1913,7 +1907,7 @@
         <v>15</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>15</v>
@@ -1922,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>15</v>
@@ -1933,19 +1927,19 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>15</v>
@@ -1957,19 +1951,19 @@
         <v>16</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>18</v>
@@ -1983,22 +1977,22 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>15</v>
@@ -2007,16 +2001,16 @@
         <v>16</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>15</v>
@@ -2025,7 +2019,7 @@
         <v>18</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>15</v>
@@ -2033,49 +2027,49 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>15</v>
@@ -2083,146 +2077,146 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P23" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O25" s="8">
         <v>0.93</v>
@@ -2236,25 +2230,25 @@
         <v>10</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>15</v>
@@ -2263,19 +2257,19 @@
         <v>15</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>15</v>
@@ -2286,34 +2280,34 @@
         <v>10</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>15</v>
@@ -2322,13 +2316,13 @@
         <v>15</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -2336,49 +2330,49 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>43</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -2386,25 +2380,25 @@
         <v>10</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>15</v>
@@ -2413,69 +2407,69 @@
         <v>15</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>15</v>
@@ -2483,19 +2477,19 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>15</v>
@@ -2504,7 +2498,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>15</v>
@@ -2513,7 +2507,7 @@
         <v>15</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>15</v>
@@ -2522,7 +2516,7 @@
         <v>15</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>15</v>
@@ -2533,37 +2527,37 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="J32" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>15</v>
@@ -2572,7 +2566,7 @@
         <v>15</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>15</v>
@@ -2583,22 +2577,22 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="D33" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>15</v>
@@ -2607,54 +2601,54 @@
         <v>16</v>
       </c>
       <c r="I33" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M33" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>15</v>
@@ -2666,45 +2660,45 @@
         <v>17</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="G35" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>15</v>
@@ -2713,27 +2707,27 @@
         <v>15</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>149</v>
@@ -2742,48 +2736,48 @@
         <v>150</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>151</v>
@@ -2792,40 +2786,40 @@
         <v>152</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>15</v>
@@ -2836,25 +2830,25 @@
         <v>10</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>15</v>
@@ -2863,19 +2857,19 @@
         <v>15</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>15</v>
@@ -2886,16 +2880,16 @@
         <v>10</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="E39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>15</v>
@@ -2907,25 +2901,25 @@
         <v>16</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>15</v>
@@ -2936,46 +2930,46 @@
         <v>10</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>15</v>
@@ -2986,19 +2980,19 @@
         <v>10</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>15</v>
@@ -3007,25 +3001,25 @@
         <v>16</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K41" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N41" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L41" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="O41" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>15</v>
@@ -3033,249 +3027,249 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="K43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="M43" s="6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G44" s="8">
         <v>0.95</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G46" s="8">
         <v>0.93</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>15</v>
@@ -3283,49 +3277,49 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>15</v>
@@ -3333,49 +3327,49 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="D48" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>15</v>
@@ -3383,19 +3377,19 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>15</v>
@@ -3404,31 +3398,31 @@
         <v>15</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
@@ -3455,40 +3449,40 @@
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
       <c r="E51" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="H51" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="G51" s="15" t="s">
+      <c r="I51" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="J51" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="K51" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="J51" s="15" t="s">
+      <c r="L51" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="K51" s="15" t="s">
+      <c r="M51" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="L51" s="15" t="s">
+      <c r="N51" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="M51" s="15" t="s">
+      <c r="O51" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="N51" s="15" t="s">
+      <c r="P51" s="15" t="s">
         <v>193</v>
-      </c>
-      <c r="O51" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="P51" s="15" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="52">
